--- a/data/trans_orig/IP07C10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34773</t>
+          <t>35518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51538</t>
+          <t>52170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60365</t>
+          <t>59560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82039</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106930</t>
+          <t>106434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>45876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62523</t>
+          <t>62661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>47872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65291</t>
+          <t>65587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100220</t>
+          <t>99249</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124131</t>
+          <t>123521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>55279</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75882</t>
+          <t>76225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56700</t>
+          <t>56115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76983</t>
+          <t>76717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117426</t>
+          <t>117091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>146473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>60858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82399</t>
+          <t>81796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56617</t>
+          <t>55825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>77154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123424</t>
+          <t>121101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153952</t>
+          <t>152874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30179</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>47235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38696</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57718</t>
+          <t>58043</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71891</t>
+          <t>72862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>98220</t>
+          <t>99623</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95089</t>
+          <t>95716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121379</t>
+          <t>121488</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104230</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130739</t>
+          <t>130986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>205767</t>
+          <t>206096</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245515</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>112991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139213</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110160</t>
+          <t>109087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137218</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231285</t>
+          <t>228288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>267085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71300</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>123741</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>47948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68917</t>
+          <t>68697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>54549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74012</t>
+          <t>75839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110432</t>
+          <t>109425</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138187</t>
+          <t>136627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>59434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78265</t>
+          <t>79708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81866</t>
+          <t>82124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125139</t>
+          <t>125918</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154175</t>
+          <t>154623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22473</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36018</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>37640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>57815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>47106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66600</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91368</t>
+          <t>90962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119128</t>
+          <t>119051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64344</t>
+          <t>63983</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84886</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62624</t>
+          <t>62080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83455</t>
+          <t>83719</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132563</t>
+          <t>131496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161763</t>
+          <t>161947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23144</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>39365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49292</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>73384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>92933</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119529</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>107868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136017</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>208698</t>
+          <t>208006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248685</t>
+          <t>246483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128681</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156157</t>
+          <t>156781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>129275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>158250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266985</t>
+          <t>265068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306529</t>
+          <t>306428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68619</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91081</t>
+          <t>91258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67972</t>
+          <t>68086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89159</t>
+          <t>89955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144612</t>
+          <t>144070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>176262</t>
+          <t>175133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66156</t>
+          <t>66251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87977</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67480</t>
+          <t>67155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89406</t>
+          <t>90431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138260</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169452</t>
+          <t>169034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,99%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21158</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27149</t>
+          <t>27749</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46087</t>
+          <t>47488</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47890</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69190</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51802</t>
+          <t>51466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72428</t>
+          <t>72886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104390</t>
+          <t>105306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134225</t>
+          <t>135018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56313</t>
+          <t>57010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76689</t>
+          <t>77358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>61630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83974</t>
+          <t>83849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125191</t>
+          <t>124070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>154032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36582</t>
+          <t>36309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37907</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44746</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67241</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7050</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125441</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>155944</t>
+          <t>156022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>259339</t>
+          <t>257749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303280</t>
+          <t>300514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127944</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>157467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>134131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165913</t>
+          <t>164874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>274137</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>313663</t>
+          <t>315800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>107927</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">

--- a/data/trans_orig/IP07C10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres, percibida por el/la menor en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50840</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42418</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59710</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35518</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52170</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35785</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51971</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>50840</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>41717</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59560</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>41,41%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82096</t>
+          <t>83027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106434</t>
+          <t>107636</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57003</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48515</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66398</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54579</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>45876</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62661</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46060</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>62595</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>49,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57003</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47872</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>65587</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99249</t>
+          <t>99621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123521</t>
+          <t>123921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12421</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7635</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18018</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9767</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5824</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15372</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15217</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,84%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12421</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7589</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18508</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30614</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1066,67 +1066,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5150</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1936</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5214</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5440</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1179,102 +1179,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3466</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4113</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4396</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4630</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122783</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122783</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122783</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110454</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110454</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110454</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122783</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122783</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122783</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66383</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56251</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77008</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>65053</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55279</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>76225</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>55648</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76501</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>36,99%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66383</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>56115</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76717</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117091</t>
+          <t>116953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146473</t>
+          <t>146379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66497</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55365</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76195</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70949</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60858</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81796</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60070</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>82135</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66497</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55825</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77154</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121101</t>
+          <t>122802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152874</t>
+          <t>152356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47211</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38066</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57253</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>25,63%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37690</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29557</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>47235</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>28922</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>47061</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>21,43%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>47211</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>38014</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>58043</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>72862</t>
+          <t>72934</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>99623</t>
+          <t>98305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8202</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>709</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4085</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8316</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1444</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4981</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1444</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5092</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184176</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184176</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184176</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>175845</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>175845</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>175845</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184176</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184176</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184176</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>117222</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>103981</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>131012</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>108491</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>95716</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>121488</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>95594</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>121574</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>37,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>117222</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>103230</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>130986</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206096</t>
+          <t>208505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245856</t>
+          <t>248169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -2199,74 +2199,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123500</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109865</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>138064</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>125529</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112991</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>139275</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112960</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>139274</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>39,46%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>48,65%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>123500</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>109087</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>137752</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,23%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>35,54%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>371</t>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228288</t>
+          <t>229092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267085</t>
+          <t>267831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59632</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>48800</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>71870</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>47457</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>38544</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>57987</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>58096</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>59632</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>49995</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>71559</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92263</t>
+          <t>92313</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>122867</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10601</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2646</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6977</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6026</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10814</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2177</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6498</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5831</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>306959</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>306959</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>306959</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>425</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>286300</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>286300</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>286300</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>306959</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>306959</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>306959</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres, percibida por el/la menor en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64869</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54720</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75313</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>58442</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47948</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>68697</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48717</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68253</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>64869</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>54549</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>75839</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,3%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109425</t>
+          <t>109829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136627</t>
+          <t>138208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71210</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81809</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>68693</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59434</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79708</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59270</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79289</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>48,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>71210</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>61170</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82124</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>125918</t>
+          <t>124637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154623</t>
+          <t>154859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11495</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6859</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17294</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,67%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9604</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9154</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21384</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,49%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11495</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7254</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17941</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -3337,92 +3337,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5949</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2227</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6049</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>149802</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>149802</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>149802</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>142030</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>142030</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>142030</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>149802</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>149802</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>149802</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56828</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>47940</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67213</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>47356</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37640</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57815</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37973</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56730</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56828</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>47106</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66857</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90962</t>
+          <t>89704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119051</t>
+          <t>117017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73166</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62782</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82624</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>73737</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63983</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85424</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62847</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84294</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,31%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>73166</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>62080</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83719</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>132538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161947</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30344</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23194</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39613</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24,12%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>30176</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22781</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39652</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22185</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38644</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>19,77%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>25,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>30344</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>22976</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39365</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73384</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8327</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3493</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3888</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1437</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7551</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4132,107 +4132,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3202</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2955</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3011</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164226</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164226</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164226</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>152633</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>152633</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>152633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>164226</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>164226</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>164226</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,107 +4362,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121697</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>107298</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>135608</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>105799</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>92933</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>119254</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>93089</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>119242</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>40,47%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>121697</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>107868</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>136365</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>227495</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>209109</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>246368</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>34,35%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>227495</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>208006</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>246483</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>144376</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>131511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>160033</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>142431</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>129014</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>156781</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>128311</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>155414</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>144376</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>129275</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>158250</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,98%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265068</t>
+          <t>266801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306428</t>
+          <t>306855</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41840</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32602</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>52334</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>45071</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>35406</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>55677</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>35575</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>55516</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>15,3%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>41840</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>32799</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>52502</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73664</t>
+          <t>73825</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101649</t>
+          <t>101053</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2871</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3848</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6115</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11061</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4814,92 +4814,92 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2980</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>314028</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>314028</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>314028</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>420</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>294663</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>294663</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>294663</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>314028</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>314028</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>314028</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres, percibida por el/la menor en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>79516</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>68535</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90890</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>79860</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>69194</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>91258</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>69055</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>90955</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,99%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>79516</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>68086</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>89955</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144070</t>
+          <t>144435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175133</t>
+          <t>177190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78022</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66153</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88986</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>45,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>76502</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>66251</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88049</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65665</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>87400</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>42,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78022</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67155</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>90431</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>45,03%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139448</t>
+          <t>138200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169034</t>
+          <t>169458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14356</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20932</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21974</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15812</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30344</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>15383</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>30420</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,28%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14356</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8980</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21074</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -5613,107 +5613,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3155</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>708</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3216</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5731,102 +5731,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3389</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>646</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3811</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4649</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>173280</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>173280</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>173280</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>178982</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>178982</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>178982</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>173280</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>173280</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>173280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61258</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50451</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71825</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>58355</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48161</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69133</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47731</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>68076</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>61258</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>51466</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>72886</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105306</t>
+          <t>105627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135018</t>
+          <t>135536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72899</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>62192</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84595</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66526</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57010</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77358</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>56589</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76840</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>72899</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61630</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>83849</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>43,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124070</t>
+          <t>123732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154032</t>
+          <t>153198</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -6187,67 +6187,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>28794</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20766</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37259</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>26783</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19776</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36309</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19267</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>34774</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28794</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21335</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37852</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>44221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68243</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9689</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3103</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1162</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6915</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1137</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7150</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9089</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4997</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2853</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6712</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7040</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6115</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168384</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168384</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>157621</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157621</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157621</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>168384</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>168384</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>168384</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>140774</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>125856</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>155319</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>138215</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>122974</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>152817</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>123007</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>153030</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>140774</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>126821</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,2%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257749</t>
+          <t>256172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300514</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>150921</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135895</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>166577</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>143028</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>128777</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>157467</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>127013</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>157645</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>42,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>150921</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>134131</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>164874</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274137</t>
+          <t>272926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315800</t>
+          <t>317012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43150</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33587</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>53515</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>48758</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>37989</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>60132</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>38762</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>60910</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,49%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43150</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33792</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>53993</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>78304</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>107927</t>
+          <t>107101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5034</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10479</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3103</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6457</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7165</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5034</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10491</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5773</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3499</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7705</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7859</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6227</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>341665</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>341665</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>341665</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>479</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>336602</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>336602</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>336602</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>341665</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>341665</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>341665</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
